--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03_A04_세부요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03_A04_세부요청표_20261028_담당자반영.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 권고일 2026-10-29</t>
+          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 권고일 2026-10-30</t>
+          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-30</t>
         </is>
       </c>
     </row>
